--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\livia\Box\liv_RETL\docs\research_proposal\Task_3_Radiative_conductivity_thin_films\PNAS\zenodo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6462561-D87D-4556-96E6-4E0EED08D888}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35A3916-29E0-494D-BE3B-3493F5D0473E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27210" windowHeight="7890" activeTab="9" xr2:uid="{EF243DA0-28C0-45C9-95DA-8A7CDC78204E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27210" windowHeight="7890" activeTab="6" xr2:uid="{EF243DA0-28C0-45C9-95DA-8A7CDC78204E}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig_2A" sheetId="1" r:id="rId1"/>
@@ -34,15 +34,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
   <si>
     <t>Temperature (K)</t>
   </si>
   <si>
-    <t>DSGF</t>
+    <t>omega 10^14 rad/s)</t>
   </si>
   <si>
-    <t>KT</t>
+    <t>D = 66 nm</t>
+  </si>
+  <si>
+    <t>D = 132 nm</t>
+  </si>
+  <si>
+    <t>omega 10^14 (rad/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D = 66 nm, Re(kz) (rad/m) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D = 132 nm, Re(kz) (rad/m) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D = 66 nm, Im(kz) (rad/m) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D = 132 nm, Im(kz) (rad/m) </t>
+  </si>
+  <si>
+    <t>DSGF (W/mK)</t>
+  </si>
+  <si>
+    <t>KT (W/mK)</t>
   </si>
   <si>
     <r>
@@ -57,54 +81,97 @@
       </rPr>
       <t>Λeff</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (W/mK)</t>
+    </r>
   </si>
   <si>
-    <t>DSGF SPhPs+BPhPs</t>
+    <t>DSGF SPhPs+BPhPs (W/mK)</t>
   </si>
   <si>
-    <t>DSGF SPhPs</t>
+    <t>DSGF SPhPs (W/mK)</t>
   </si>
   <si>
-    <t>DSGF BPhPs</t>
+    <t>DSGF BPhPs (W/mK)</t>
   </si>
   <si>
-    <t>omega 10^14 rad/s)</t>
+    <t xml:space="preserve">SiO2 light line  (rad/m) </t>
   </si>
   <si>
-    <t xml:space="preserve">D = 66 nm, Re(kz) rad/m </t>
+    <t>D = 66 nm, Λ (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">D = 132 nm, Re(kz) rad/m </t>
+    <t>D = 66 nm, Λeff (m)</t>
   </si>
   <si>
-    <t>SiO2 light line</t>
+    <t>D = 132 nm, Λ (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">D = 66 nm, Im(kz) rad/m </t>
+    <t>D = 132 nm, Λeff (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">D = 132 nm, Im(kz) rad/m </t>
+    <t>DSGF (W m^(-1)K^(-1) (rad/s)^(-1))</t>
   </si>
   <si>
-    <t xml:space="preserve">DSGF </t>
+    <t>KT  (W m^(-1)K^(-1) (rad/s)^(-1))</t>
   </si>
   <si>
-    <t>D = 66 nm</t>
+    <r>
+      <t xml:space="preserve">KT with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Λeff</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  (W m^(-1)K^(-1) (rad/s)^(-1))</t>
+    </r>
   </si>
   <si>
-    <t>D = 132 nm</t>
+    <t>KT (W m^(-1)K^(-1) (rad/s)^(-1))</t>
   </si>
   <si>
-    <t xml:space="preserve">D = 66 nm, Λeff </t>
-  </si>
-  <si>
-    <t xml:space="preserve">D = 66 nm, Λ </t>
-  </si>
-  <si>
-    <t>D = 132 nm, Λ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D = 132 nm, Λeff </t>
+    <r>
+      <t xml:space="preserve">KT with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Λeff</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (W m^(-1)K^(-1) (rad/s)^(-1))</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -146,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -157,6 +224,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -487,13 +557,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -585,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -657,7 +727,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -665,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -757,7 +827,7 @@
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -766,13 +836,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -867,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -965,16 +1035,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2577,16 +2647,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -4178,24 +4248,24 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE448615-653B-4713-AE20-AA2501E2D66C}">
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="24.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
       </c>
       <c r="D1" t="s">
         <v>18</v>
@@ -4204,78 +4274,1570 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B80" s="1"/>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0.77900000000000003</v>
+      </c>
+      <c r="B2" s="1">
+        <v>4.4721699999999997E-6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>6.4803699999999999E-8</v>
+      </c>
+      <c r="D2" s="1">
+        <v>4.4721699999999997E-6</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1.27296E-7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2.1666799999999998E-6</v>
+      </c>
+      <c r="C3" s="1">
+        <v>6.3575499999999999E-8</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2.1666799999999998E-6</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1.2263200000000001E-7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0.82</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1.83968E-6</v>
+      </c>
+      <c r="C4" s="1">
+        <v>6.3162400000000002E-8</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.83968E-6</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.2109899999999999E-7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1.56258E-6</v>
+      </c>
+      <c r="C5" s="1">
+        <v>6.2683400000000001E-8</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.56258E-6</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.1934400000000001E-7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0.83399999999999996</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1.3348300000000001E-6</v>
+      </c>
+      <c r="C6" s="1">
+        <v>6.2149199999999994E-8</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.3348300000000001E-6</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1.1741299999999999E-7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1.1333100000000001E-6</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6.1509199999999996E-8</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1.1333100000000001E-6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1.1513699999999999E-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>0.85</v>
+      </c>
+      <c r="B8" s="1">
+        <v>9.9065499999999992E-7</v>
+      </c>
+      <c r="C8" s="1">
+        <v>6.0910299999999997E-8</v>
+      </c>
+      <c r="D8" s="1">
+        <v>9.9065499999999992E-7</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1.13042E-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="B9" s="1">
+        <v>9.0899899999999997E-7</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6.0489700000000005E-8</v>
+      </c>
+      <c r="D9" s="1">
+        <v>9.0899899999999997E-7</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1.11591E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="B10" s="1">
+        <v>8.5712199999999999E-7</v>
+      </c>
+      <c r="C10" s="1">
+        <v>6.01844E-8</v>
+      </c>
+      <c r="D10" s="1">
+        <v>8.5712199999999999E-7</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1.10548E-7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>0.87</v>
+      </c>
+      <c r="B11" s="1">
+        <v>8.4308900000000004E-7</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1">
+        <v>8.4308900000000004E-7</v>
+      </c>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>0.87070999999999998</v>
+      </c>
+      <c r="B12" s="1">
+        <v>8.4206900000000005E-7</v>
+      </c>
+      <c r="D12" s="1">
+        <v>8.4206900000000005E-7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0.87143000000000004</v>
+      </c>
+      <c r="B13" s="1">
+        <v>8.4127800000000002E-7</v>
+      </c>
+      <c r="D13" s="1">
+        <v>8.4127800000000002E-7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>0.87214000000000003</v>
+      </c>
+      <c r="B14" s="1">
+        <v>8.4070899999999999E-7</v>
+      </c>
+      <c r="D14" s="1">
+        <v>8.4070899999999999E-7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>0.87285999999999997</v>
+      </c>
+      <c r="B15" s="1">
+        <v>8.4035700000000001E-7</v>
+      </c>
+      <c r="D15" s="1">
+        <v>8.4035700000000001E-7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>0.87356999999999996</v>
+      </c>
+      <c r="B16" s="1">
+        <v>8.4021500000000001E-7</v>
+      </c>
+      <c r="D16" s="1">
+        <v>8.5524099999999998E-8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>0.87429000000000001</v>
+      </c>
+      <c r="B17" s="1">
+        <v>8.4027899999999998E-7</v>
+      </c>
+      <c r="D17" s="1">
+        <v>8.5059200000000005E-8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0.875</v>
+      </c>
+      <c r="B18" s="1">
+        <v>8.4054299999999996E-7</v>
+      </c>
+      <c r="D18" s="1">
+        <v>8.4586800000000004E-8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>0.87570999999999999</v>
+      </c>
+      <c r="B19" s="1">
+        <v>8.4100200000000003E-7</v>
+      </c>
+      <c r="D19" s="1">
+        <v>8.4107300000000003E-8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>0.87643000000000004</v>
+      </c>
+      <c r="B20" s="1">
+        <v>8.4165100000000005E-7</v>
+      </c>
+      <c r="D20" s="1">
+        <v>8.3620700000000002E-8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>0.87714000000000003</v>
+      </c>
+      <c r="B21" s="1">
+        <v>8.4248600000000002E-7</v>
+      </c>
+      <c r="D21" s="1">
+        <v>8.3127199999999998E-8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>0.87785999999999997</v>
+      </c>
+      <c r="B22" s="1">
+        <v>8.4350099999999998E-7</v>
+      </c>
+      <c r="D22" s="1">
+        <v>8.4350099999999998E-7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>0.87856999999999996</v>
+      </c>
+      <c r="B23" s="1">
+        <v>8.44691E-7</v>
+      </c>
+      <c r="D23" s="1">
+        <v>8.44691E-7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>0.87929000000000002</v>
+      </c>
+      <c r="B24" s="1">
+        <v>8.4605400000000004E-7</v>
+      </c>
+      <c r="D24" s="1">
+        <v>8.4605400000000004E-7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>0.88</v>
+      </c>
+      <c r="B25" s="1">
+        <v>8.4758400000000003E-7</v>
+      </c>
+      <c r="D25" s="1">
+        <v>8.4758400000000003E-7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>0.88021000000000005</v>
+      </c>
+      <c r="B26" s="1">
+        <v>8.4806599999999999E-7</v>
+      </c>
+      <c r="D26" s="1">
+        <v>8.4806599999999999E-7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>0.88532</v>
+      </c>
+      <c r="B27" s="1">
+        <v>8.6384800000000005E-7</v>
+      </c>
+      <c r="D27" s="1">
+        <v>8.6384800000000005E-7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>0.89041999999999999</v>
+      </c>
+      <c r="B28" s="1">
+        <v>8.8668599999999995E-7</v>
+      </c>
+      <c r="D28" s="1">
+        <v>8.8668599999999995E-7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>0.89553000000000005</v>
+      </c>
+      <c r="B29" s="1">
+        <v>9.1567699999999997E-7</v>
+      </c>
+      <c r="D29" s="1">
+        <v>9.1567699999999997E-7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>0.90063000000000004</v>
+      </c>
+      <c r="B30" s="1">
+        <v>9.50226E-7</v>
+      </c>
+      <c r="D30" s="1">
+        <v>9.50226E-7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>0.90573999999999999</v>
+      </c>
+      <c r="B31" s="1">
+        <v>9.9000800000000006E-7</v>
+      </c>
+      <c r="D31" s="1">
+        <v>9.9000800000000006E-7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>0.91083999999999998</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1.03493E-6</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1.03493E-6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>0.91595000000000004</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1.0851E-6</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1.0851E-6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>0.92105000000000004</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1.1408200000000001E-6</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1.1408200000000001E-6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>0.92615999999999998</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1.2025900000000001E-6</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1.2025900000000001E-6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>0.93125999999999998</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1.2711E-6</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1.2711E-6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>0.93637000000000004</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1.3472500000000001E-6</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1.3472500000000001E-6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>0.94147000000000003</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1.43216E-6</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1.43216E-6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>0.94657999999999998</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1.5271899999999999E-6</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1.5271899999999999E-6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>0.95167999999999997</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1.63395E-6</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1.63395E-6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>0.95679000000000003</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1.75426E-6</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1.75426E-6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>0.96189000000000002</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1.89011E-6</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1.89011E-6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="B43" s="1">
+        <v>2.04356E-6</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1">
+        <v>2.04356E-6</v>
+      </c>
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>0.97399999999999998</v>
+      </c>
+      <c r="B44" s="1">
+        <v>2.2859899999999999E-6</v>
+      </c>
+      <c r="C44" s="1">
+        <v>6.3697799999999995E-8</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2.2859899999999999E-6</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1.2309E-7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2.7026600000000001E-6</v>
+      </c>
+      <c r="C45" s="1">
+        <v>6.4042699999999997E-8</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2.7026600000000001E-6</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1.2438699999999999E-7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>0.995</v>
+      </c>
+      <c r="B46" s="1">
+        <v>3.2579900000000001E-6</v>
+      </c>
+      <c r="C46" s="1">
+        <v>6.4368400000000006E-8</v>
+      </c>
+      <c r="D46" s="1">
+        <v>3.2579900000000001E-6</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1.2562499999999999E-7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1.01</v>
+      </c>
+      <c r="B47" s="1">
+        <v>4.15937E-6</v>
+      </c>
+      <c r="C47" s="1">
+        <v>6.4715400000000003E-8</v>
+      </c>
+      <c r="D47" s="1">
+        <v>4.15937E-6</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1.2695599999999999E-7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1.03</v>
+      </c>
+      <c r="B48" s="1">
+        <v>5.5536999999999999E-6</v>
+      </c>
+      <c r="C48" s="1">
+        <v>6.5033400000000006E-8</v>
+      </c>
+      <c r="D48" s="1">
+        <v>5.5536999999999999E-6</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1.2818700000000001E-7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1.05</v>
+      </c>
+      <c r="B49" s="1">
+        <v>7.0957800000000002E-6</v>
+      </c>
+      <c r="C49" s="1">
+        <v>6.52411E-8</v>
+      </c>
+      <c r="D49" s="1">
+        <v>7.0957800000000002E-6</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1.28998E-7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1.04174E-5</v>
+      </c>
+      <c r="C50" s="1">
+        <v>6.5481300000000005E-8</v>
+      </c>
+      <c r="D50" s="1">
+        <v>1.04174E-5</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1.2994100000000001E-7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1.37821E-5</v>
+      </c>
+      <c r="C51" s="1">
+        <v>6.5607199999999997E-8</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1.37821E-5</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1.3043799999999999E-7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1.21</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1.9360200000000001E-5</v>
+      </c>
+      <c r="C52" s="1">
+        <v>6.5719900000000003E-8</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1.9360200000000001E-5</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1.30884E-7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1.28</v>
+      </c>
+      <c r="B53" s="1">
+        <v>2.13932E-5</v>
+      </c>
+      <c r="C53" s="1">
+        <v>6.5746399999999994E-8</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2.13932E-5</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1.3098900000000001E-7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1.32</v>
+      </c>
+      <c r="B54" s="1">
+        <v>2.0805599999999999E-5</v>
+      </c>
+      <c r="C54" s="1">
+        <v>6.5739299999999994E-8</v>
+      </c>
+      <c r="D54" s="1">
+        <v>2.0805599999999999E-5</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1.30961E-7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1.36</v>
+      </c>
+      <c r="B55" s="1">
+        <v>1.8716199999999999E-5</v>
+      </c>
+      <c r="C55" s="1">
+        <v>6.57103E-8</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1.8716199999999999E-5</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1.3084600000000001E-7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>1.38</v>
+      </c>
+      <c r="B56" s="1">
+        <v>1.7075199999999999E-5</v>
+      </c>
+      <c r="C56" s="1">
+        <v>6.5682599999999998E-8</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1.7075199999999999E-5</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1.3073599999999999E-7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1.4</v>
+      </c>
+      <c r="B57" s="1">
+        <v>1.50424E-5</v>
+      </c>
+      <c r="C57" s="1">
+        <v>6.5639900000000005E-8</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1.50424E-5</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1.3056700000000001E-7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>1.42</v>
+      </c>
+      <c r="B58" s="1">
+        <v>1.2660099999999999E-5</v>
+      </c>
+      <c r="C58" s="1">
+        <v>6.5572600000000006E-8</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1.2660099999999999E-5</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1.30301E-7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1.46</v>
+      </c>
+      <c r="B59" s="1">
+        <v>7.3911299999999998E-6</v>
+      </c>
+      <c r="C59" s="1">
+        <v>6.5271099999999995E-8</v>
+      </c>
+      <c r="D59" s="1">
+        <v>7.3911299999999998E-6</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1.29115E-7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1.49</v>
+      </c>
+      <c r="B60" s="1">
+        <v>4.2099199999999998E-6</v>
+      </c>
+      <c r="C60" s="1">
+        <v>6.4730499999999999E-8</v>
+      </c>
+      <c r="D60" s="1">
+        <v>4.2099199999999998E-6</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1.27014E-7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1.51</v>
+      </c>
+      <c r="B61" s="1">
+        <v>3.26222E-6</v>
+      </c>
+      <c r="C61" s="1">
+        <v>6.4370399999999995E-8</v>
+      </c>
+      <c r="D61" s="1">
+        <v>3.26222E-6</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1.25633E-7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1.53</v>
+      </c>
+      <c r="B62" s="1">
+        <v>3.5173600000000002E-6</v>
+      </c>
+      <c r="C62" s="1">
+        <v>6.4485999999999999E-8</v>
+      </c>
+      <c r="D62" s="1">
+        <v>3.5173600000000002E-6</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1.26075E-7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1.56</v>
+      </c>
+      <c r="B63" s="1">
+        <v>5.59912E-6</v>
+      </c>
+      <c r="C63" s="1">
+        <v>6.5041099999999999E-8</v>
+      </c>
+      <c r="D63" s="1">
+        <v>5.59912E-6</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1.2821699999999999E-7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>1.59</v>
+      </c>
+      <c r="B64" s="1">
+        <v>8.0831599999999997E-6</v>
+      </c>
+      <c r="C64" s="1">
+        <v>6.5332900000000001E-8</v>
+      </c>
+      <c r="D64" s="1">
+        <v>8.0831599999999997E-6</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1.2935700000000001E-7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>1.61</v>
+      </c>
+      <c r="B65" s="1">
+        <v>9.2693699999999993E-6</v>
+      </c>
+      <c r="C65" s="1">
+        <v>6.5417600000000002E-8</v>
+      </c>
+      <c r="D65" s="1">
+        <v>9.2693699999999993E-6</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1.2968999999999999E-7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1.64</v>
+      </c>
+      <c r="B66" s="1">
+        <v>1.0097399999999999E-5</v>
+      </c>
+      <c r="C66" s="1">
+        <v>6.5464900000000005E-8</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1.0097399999999999E-5</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1.2987599999999999E-7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1.67</v>
+      </c>
+      <c r="B67" s="1">
+        <v>9.9934600000000007E-6</v>
+      </c>
+      <c r="C67" s="1">
+        <v>6.5459399999999999E-8</v>
+      </c>
+      <c r="D67" s="1">
+        <v>9.9934600000000007E-6</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1.2985499999999999E-7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>1.7</v>
+      </c>
+      <c r="B68" s="1">
+        <v>9.2962700000000007E-6</v>
+      </c>
+      <c r="C68" s="1">
+        <v>6.5419199999999996E-8</v>
+      </c>
+      <c r="D68" s="1">
+        <v>9.2962700000000007E-6</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1.29696E-7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1.73</v>
+      </c>
+      <c r="B69" s="1">
+        <v>8.2781100000000003E-6</v>
+      </c>
+      <c r="C69" s="1">
+        <v>6.5348499999999998E-8</v>
+      </c>
+      <c r="D69" s="1">
+        <v>8.2781100000000003E-6</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1.29418E-7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1.77</v>
+      </c>
+      <c r="B70" s="1">
+        <v>6.7252899999999999E-6</v>
+      </c>
+      <c r="C70" s="1">
+        <v>6.5199800000000004E-8</v>
+      </c>
+      <c r="D70" s="1">
+        <v>6.7252899999999999E-6</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1.28836E-7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>1.8</v>
+      </c>
+      <c r="B71" s="1">
+        <v>5.5518400000000002E-6</v>
+      </c>
+      <c r="C71" s="1">
+        <v>6.5032999999999997E-8</v>
+      </c>
+      <c r="D71" s="1">
+        <v>5.5518400000000002E-6</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1.2818600000000001E-7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>1.84</v>
+      </c>
+      <c r="B72" s="1">
+        <v>4.0902100000000001E-6</v>
+      </c>
+      <c r="C72" s="1">
+        <v>6.4694100000000002E-8</v>
+      </c>
+      <c r="D72" s="1">
+        <v>4.0902100000000001E-6</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1.26874E-7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1.87</v>
+      </c>
+      <c r="B73" s="1">
+        <v>3.1149999999999998E-6</v>
+      </c>
+      <c r="C73" s="1">
+        <v>6.4295299999999997E-8</v>
+      </c>
+      <c r="D73" s="1">
+        <v>3.1149999999999998E-6</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1.2534599999999999E-7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>1.91</v>
+      </c>
+      <c r="B74" s="1">
+        <v>2.0128200000000002E-6</v>
+      </c>
+      <c r="C74" s="1">
+        <v>6.3397200000000006E-8</v>
+      </c>
+      <c r="D74" s="1">
+        <v>2.0128200000000002E-6</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1.21968E-7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>1.95269</v>
+      </c>
+      <c r="B75" s="1">
+        <v>1.1155900000000001E-6</v>
+      </c>
+      <c r="C75" s="1">
+        <v>6.1442599999999995E-8</v>
+      </c>
+      <c r="D75" s="1">
+        <v>1.1155900000000001E-6</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1.1490200000000001E-7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1.98</v>
+      </c>
+      <c r="B76" s="1">
+        <v>7.0726000000000005E-7</v>
+      </c>
+      <c r="C76" s="1">
+        <v>5.9075999999999999E-8</v>
+      </c>
+      <c r="D76" s="1">
+        <v>7.0726000000000005E-7</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1.06833E-7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>1.99</v>
+      </c>
+      <c r="B77" s="1">
+        <v>5.9267799999999998E-7</v>
+      </c>
+      <c r="C77" s="1">
+        <v>5.7894899999999998E-8</v>
+      </c>
+      <c r="D77" s="1">
+        <v>5.9267799999999998E-7</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1.0299E-7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2</v>
+      </c>
+      <c r="B78" s="1">
+        <v>4.9767199999999998E-7</v>
+      </c>
+      <c r="C78" s="1">
+        <v>5.6559700000000002E-8</v>
+      </c>
+      <c r="D78" s="1">
+        <v>4.9767199999999998E-7</v>
+      </c>
+      <c r="E78" s="1">
+        <v>9.8783700000000003E-8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>2.02583</v>
+      </c>
+      <c r="B79" s="1">
+        <v>3.42379E-7</v>
+      </c>
+      <c r="C79" s="1">
+        <v>5.30802E-8</v>
+      </c>
+      <c r="D79" s="1">
+        <v>3.42379E-7</v>
+      </c>
+      <c r="E79" s="1">
+        <v>8.8459800000000002E-8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2.04</v>
+      </c>
+      <c r="B80" s="1">
+        <v>3.0595000000000001E-7</v>
+      </c>
       <c r="C80" s="1"/>
-    </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B81" s="1"/>
+      <c r="D80" s="1">
+        <v>1.10834E-7</v>
+      </c>
+      <c r="E80" s="1"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>2.0512000000000001</v>
+      </c>
+      <c r="B81" s="1">
+        <v>5.5085799999999997E-8</v>
+      </c>
       <c r="C81" s="1"/>
-    </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B82" s="1"/>
+      <c r="D81" s="1">
+        <v>1.10733E-7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>2.0623999999999998</v>
+      </c>
+      <c r="B82" s="1">
+        <v>5.4522899999999999E-8</v>
+      </c>
       <c r="C82" s="1"/>
-    </row>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D88" s="1"/>
-    </row>
-    <row r="89" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D89" s="1"/>
-    </row>
-    <row r="90" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D90" s="1"/>
-    </row>
-    <row r="91" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D91" s="1"/>
-    </row>
-    <row r="92" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D92" s="1"/>
-    </row>
-    <row r="93" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D93" s="1"/>
-    </row>
-    <row r="94" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D94" s="1"/>
+      <c r="D82" s="1">
+        <v>1.0951099999999999E-7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>2.0735999999999999</v>
+      </c>
+      <c r="B83" s="1">
+        <v>5.3462199999999997E-8</v>
+      </c>
+      <c r="D83" s="1">
+        <v>1.07301E-7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>2.0848</v>
+      </c>
+      <c r="B84" s="1">
+        <v>5.2000500000000003E-8</v>
+      </c>
+      <c r="D84" s="1">
+        <v>1.04302E-7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="B85" s="1">
+        <v>5.0242500000000001E-8</v>
+      </c>
+      <c r="D85" s="1">
+        <v>1.00724E-7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>2.1072000000000002</v>
+      </c>
+      <c r="B86" s="1">
+        <v>4.8285599999999998E-8</v>
+      </c>
+      <c r="D86" s="1">
+        <v>9.6760899999999997E-8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>2.1183999999999998</v>
+      </c>
+      <c r="B87" s="1">
+        <v>4.6214199999999997E-8</v>
+      </c>
+      <c r="D87" s="1">
+        <v>9.2579400000000006E-8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>2.1295999999999999</v>
+      </c>
+      <c r="B88" s="1">
+        <v>4.41004E-8</v>
+      </c>
+      <c r="D88" s="1">
+        <v>8.8321300000000004E-8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>2.1408</v>
+      </c>
+      <c r="B89" s="1">
+        <v>4.2005200000000002E-8</v>
+      </c>
+      <c r="D89" s="1">
+        <v>8.4107E-8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>2.1520000000000001</v>
+      </c>
+      <c r="B90" s="1">
+        <v>3.9981800000000003E-8</v>
+      </c>
+      <c r="D90" s="1">
+        <v>8.0040999999999995E-8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>2.1631999999999998</v>
+      </c>
+      <c r="B91" s="1">
+        <v>3.8077200000000002E-8</v>
+      </c>
+      <c r="D91" s="1">
+        <v>7.6216800000000003E-8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>2.1743999999999999</v>
+      </c>
+      <c r="B92" s="1">
+        <v>3.6335900000000003E-8</v>
+      </c>
+      <c r="D92" s="1">
+        <v>7.2721900000000002E-8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>2.1856</v>
+      </c>
+      <c r="B93" s="1">
+        <v>3.4801100000000001E-8</v>
+      </c>
+      <c r="D93" s="1">
+        <v>6.9642499999999996E-8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>2.1907700000000001</v>
+      </c>
+      <c r="B94" s="1">
+        <v>3.4174800000000002E-8</v>
+      </c>
+      <c r="D94" s="1">
+        <v>6.8386000000000001E-8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="B95" s="1">
+        <v>3.1875699999999997E-8</v>
+      </c>
+      <c r="D95" s="1">
+        <v>6.2880400000000002E-7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>2.2303999999999999</v>
+      </c>
+      <c r="B96" s="1">
+        <v>6.6903700000000004E-7</v>
+      </c>
+      <c r="D96" s="1">
+        <v>6.6903700000000004E-7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>2.2333099999999999</v>
+      </c>
+      <c r="B97" s="1">
+        <v>6.8108100000000004E-7</v>
+      </c>
+      <c r="D97" s="1">
+        <v>6.8108100000000004E-7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>2.2416</v>
+      </c>
+      <c r="B98" s="1">
+        <v>7.17561E-7</v>
+      </c>
+      <c r="D98" s="1">
+        <v>7.17561E-7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>2.2528000000000001</v>
+      </c>
+      <c r="B99" s="1">
+        <v>7.7280400000000004E-7</v>
+      </c>
+      <c r="D99" s="1">
+        <v>7.7280400000000004E-7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="B100" s="1">
+        <v>8.1268300000000003E-7</v>
+      </c>
+      <c r="D100" s="1">
+        <v>8.1268300000000003E-7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>2.2639999999999998</v>
+      </c>
+      <c r="B101" s="1">
+        <v>8.3657299999999996E-7</v>
+      </c>
+      <c r="D101" s="1">
+        <v>8.3657299999999996E-7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>2.2751999999999999</v>
+      </c>
+      <c r="B102" s="1">
+        <v>9.1128400000000005E-7</v>
+      </c>
+      <c r="D102" s="1">
+        <v>9.1128400000000005E-7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>2.2864</v>
+      </c>
+      <c r="B103" s="1">
+        <v>1.0001599999999999E-6</v>
+      </c>
+      <c r="D103" s="1">
+        <v>1.0001599999999999E-6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>2.29</v>
+      </c>
+      <c r="B104" s="1">
+        <v>1.03239E-6</v>
+      </c>
+      <c r="D104" s="1">
+        <v>1.03239E-6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>2.2976000000000001</v>
+      </c>
+      <c r="B105" s="1">
+        <v>1.1073899999999999E-6</v>
+      </c>
+      <c r="D105" s="1">
+        <v>1.1073899999999999E-6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>2.3088000000000002</v>
+      </c>
+      <c r="B106" s="1">
+        <v>1.23813E-6</v>
+      </c>
+      <c r="D106" s="1">
+        <v>1.23813E-6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="B107" s="1">
+        <v>1.39794E-6</v>
+      </c>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1">
+        <v>1.39794E-6</v>
+      </c>
+      <c r="E107" s="1"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>2.33</v>
+      </c>
+      <c r="B108" s="1">
+        <v>1.5689999999999999E-6</v>
+      </c>
+      <c r="C108" s="1">
+        <v>6.2696299999999997E-8</v>
+      </c>
+      <c r="D108" s="1">
+        <v>1.5689999999999999E-6</v>
+      </c>
+      <c r="E108" s="1">
+        <v>1.1939099999999999E-7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>2.3456800000000002</v>
+      </c>
+      <c r="B109" s="1">
+        <v>1.89367E-6</v>
+      </c>
+      <c r="C109" s="1">
+        <v>6.3240000000000002E-8</v>
+      </c>
+      <c r="D109" s="1">
+        <v>1.89367E-6</v>
+      </c>
+      <c r="E109" s="1">
+        <v>1.21386E-7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>2.415</v>
+      </c>
+      <c r="B110" s="1">
+        <v>3.88012E-6</v>
+      </c>
+      <c r="C110" s="1">
+        <v>6.46248E-8</v>
+      </c>
+      <c r="D110" s="1">
+        <v>3.88012E-6</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1.2660699999999999E-7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>2.4699499999999999</v>
+      </c>
+      <c r="B111" s="1">
+        <v>5.7682899999999996E-6</v>
+      </c>
+      <c r="C111" s="1">
+        <v>6.5068800000000001E-8</v>
+      </c>
+      <c r="D111" s="1">
+        <v>5.7682899999999996E-6</v>
+      </c>
+      <c r="E111" s="1">
+        <v>1.2832500000000001E-7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>2.5</v>
+      </c>
+      <c r="B112" s="1">
+        <v>6.88461E-6</v>
+      </c>
+      <c r="C112" s="1">
+        <v>6.5218100000000001E-8</v>
+      </c>
+      <c r="D112" s="1">
+        <v>6.88461E-6</v>
+      </c>
+      <c r="E112" s="1">
+        <v>1.2890800000000001E-7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>3.0322200000000001</v>
+      </c>
+      <c r="B113" s="1">
+        <v>3.4866100000000001E-5</v>
+      </c>
+      <c r="C113" s="1">
+        <v>6.5844200000000001E-8</v>
+      </c>
+      <c r="D113" s="1">
+        <v>3.4866100000000001E-5</v>
+      </c>
+      <c r="E113" s="1">
+        <v>1.31378E-7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>3.4856400000000001</v>
+      </c>
+      <c r="B114" s="1">
+        <v>6.8319100000000001E-5</v>
+      </c>
+      <c r="C114" s="1">
+        <v>6.5920400000000006E-8</v>
+      </c>
+      <c r="D114" s="1">
+        <v>6.8319100000000001E-5</v>
+      </c>
+      <c r="E114" s="1">
+        <v>1.31682E-7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4295,29 +5857,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="A1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -6010,29 +7572,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="A1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
